--- a/r4-core-96-dead-code-removal/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r4-core-96-dead-code-removal/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:26:41+00:00</t>
+    <t>2024-11-22T08:22:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
